--- a/config/Coding/MHU CDS Coding.xlsx
+++ b/config/Coding/MHU CDS Coding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\CODINGTOOL\config\Coding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C89B829-53D6-405E-85F0-83BF83AE4956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD6714B-FEBC-469F-9A6E-390194B560D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{51A74C21-A0EF-4DDE-8C1B-70F6BE272DAF}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23232" windowHeight="12432" xr2:uid="{51A74C21-A0EF-4DDE-8C1B-70F6BE272DAF}"/>
   </bookViews>
   <sheets>
     <sheet name="CDS Coding" sheetId="1" r:id="rId1"/>
@@ -2475,9 +2475,6 @@
     <t>8</t>
   </si>
   <si>
-    <t>from 2000 to 2099</t>
-  </si>
-  <si>
     <t>Vehicle Name</t>
   </si>
   <si>
@@ -3021,6 +3018,9 @@
   </si>
   <si>
     <t>Driver Occupant detection &amp; Seatbelt Reminder</t>
+  </si>
+  <si>
+    <t>2000|2099</t>
   </si>
 </sst>
 </file>
@@ -5231,7 +5231,7 @@
       <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3" refreshError="1"/>
       <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="5" refreshError="1">
         <row r="2">
           <cell r="A2" t="str">
             <v>00</v>
@@ -5749,7 +5749,7 @@
       <sheetData sheetId="9" refreshError="1"/>
       <sheetData sheetId="10" refreshError="1"/>
       <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12"/>
+      <sheetData sheetId="12" refreshError="1"/>
       <sheetData sheetId="13" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
@@ -6731,19 +6731,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="7" customFormat="1">
@@ -6792,12 +6792,12 @@
         <v>4</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="11" customFormat="1" ht="262.2">
       <c r="A5" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="5">
         <v>13</v>
@@ -6809,12 +6809,12 @@
         <v>8</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="11" customFormat="1" ht="179.4">
       <c r="A6" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="5">
         <v>14</v>
@@ -6826,12 +6826,12 @@
         <v>8</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="11" customFormat="1" ht="345">
       <c r="A7" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="5">
         <v>15</v>
@@ -6843,12 +6843,12 @@
         <v>8</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="17" customFormat="1" ht="198.6" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="5">
         <v>16</v>
@@ -6860,12 +6860,12 @@
         <v>8</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="11" customFormat="1" ht="69">
       <c r="A9" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="16">
         <v>17</v>
@@ -6877,12 +6877,12 @@
         <v>4</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="11" customFormat="1" ht="110.4">
       <c r="A10" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="5">
         <v>17</v>
@@ -6894,12 +6894,12 @@
         <v>4</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="11" customFormat="1" ht="69">
       <c r="A11" s="23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="24">
         <v>18</v>
@@ -6911,12 +6911,12 @@
         <v>4</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="11" customFormat="1" ht="55.2">
       <c r="A12" s="23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="24">
         <v>18</v>
@@ -6928,12 +6928,12 @@
         <v>4</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="11" customFormat="1" ht="82.8">
       <c r="A13" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="24">
         <v>19</v>
@@ -6945,12 +6945,12 @@
         <v>4</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="11" customFormat="1" ht="69">
       <c r="A14" s="23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="24">
         <v>19</v>
@@ -6962,12 +6962,12 @@
         <v>4</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="11" customFormat="1" ht="69">
       <c r="A15" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="24">
         <v>20</v>
@@ -6979,12 +6979,12 @@
         <v>4</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="11" customFormat="1" ht="82.8">
+    <row r="16" spans="1:5" s="11" customFormat="1" ht="69">
       <c r="A16" s="27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="24">
         <v>20</v>
@@ -6996,12 +6996,12 @@
         <v>4</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="11" customFormat="1" ht="82.8">
       <c r="A17" s="28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="29">
         <v>21</v>
@@ -7013,12 +7013,12 @@
         <v>4</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="11" customFormat="1" ht="69">
       <c r="A18" s="28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="29">
         <v>21</v>
@@ -7030,12 +7030,12 @@
         <v>4</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="11" customFormat="1" ht="69">
       <c r="A19" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="29">
         <v>22</v>
@@ -7047,12 +7047,12 @@
         <v>4</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="11" customFormat="1" ht="69">
       <c r="A20" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" s="29">
         <v>22</v>
@@ -7064,12 +7064,12 @@
         <v>4</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="11" customFormat="1" ht="143.55000000000001" customHeight="1">
       <c r="A21" s="53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21" s="31">
         <v>23</v>
@@ -7081,12 +7081,12 @@
         <v>4</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="11" customFormat="1" ht="84" customHeight="1">
       <c r="A22" s="53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="31">
         <v>23</v>
@@ -7098,12 +7098,12 @@
         <v>4</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="11" customFormat="1" ht="81.599999999999994" customHeight="1">
       <c r="A23" s="53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="31">
         <v>24</v>
@@ -7115,12 +7115,12 @@
         <v>4</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="11" customFormat="1" ht="113.55" customHeight="1">
       <c r="A24" s="53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="31">
         <v>24</v>
@@ -7132,12 +7132,12 @@
         <v>4</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="11" customFormat="1" ht="96.6">
       <c r="A25" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" s="29">
         <v>25</v>
@@ -7149,12 +7149,12 @@
         <v>4</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="11" customFormat="1" ht="69">
       <c r="A26" s="36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="29">
         <v>25</v>
@@ -7166,12 +7166,12 @@
         <v>4</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A27" s="37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="31">
         <v>26</v>
@@ -7183,12 +7183,12 @@
         <v>4</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A28" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="31">
         <v>26</v>
@@ -7200,12 +7200,12 @@
         <v>4</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A29" s="37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="31">
         <v>27</v>
@@ -7217,12 +7217,12 @@
         <v>4</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="11" customFormat="1" ht="79.2">
       <c r="A30" s="39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="31">
         <v>27</v>
@@ -7234,12 +7234,12 @@
         <v>4</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="11" customFormat="1" ht="79.2">
       <c r="A31" s="39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" s="31">
         <v>28</v>
@@ -7251,12 +7251,12 @@
         <v>4</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A32" s="39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="31">
         <v>28</v>
@@ -7268,12 +7268,12 @@
         <v>4</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="11" customFormat="1" ht="96.6">
       <c r="A33" s="41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" s="31">
         <v>29</v>
@@ -7285,12 +7285,12 @@
         <v>4</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:5" s="11" customFormat="1" ht="165.6">
       <c r="A34" s="42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="31">
         <v>29</v>
@@ -7302,12 +7302,12 @@
         <v>4</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A35" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="31">
         <v>30</v>
@@ -7319,12 +7319,12 @@
         <v>4</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A36" s="43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" s="31">
         <v>30</v>
@@ -7336,12 +7336,12 @@
         <v>4</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:5" s="11" customFormat="1" ht="169.95" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="31">
         <v>31</v>
@@ -7353,12 +7353,12 @@
         <v>4</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:5" s="11" customFormat="1" ht="79.95" customHeight="1">
       <c r="A38" s="46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="31">
         <v>31</v>
@@ -7370,12 +7370,12 @@
         <v>4</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A39" s="46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="31">
         <v>32</v>
@@ -7387,12 +7387,12 @@
         <v>4</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A40" s="43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="31">
         <v>32</v>
@@ -7404,12 +7404,12 @@
         <v>4</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A41" s="36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="31">
         <v>33</v>
@@ -7421,12 +7421,12 @@
         <v>4</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:5" s="11" customFormat="1" ht="66">
       <c r="A42" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="31">
         <v>33</v>
@@ -7438,12 +7438,12 @@
         <v>4</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:5" s="11" customFormat="1" ht="83.55" customHeight="1">
       <c r="A43" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="31">
         <v>34</v>
@@ -7455,12 +7455,12 @@
         <v>4</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:5" s="11" customFormat="1" ht="83.55" customHeight="1">
       <c r="A44" s="36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="31">
         <v>34</v>
@@ -7472,12 +7472,12 @@
         <v>4</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:5" s="11" customFormat="1" ht="83.55" customHeight="1">
       <c r="A45" s="36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" s="31">
         <v>35</v>
@@ -7489,12 +7489,12 @@
         <v>4</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:5" s="11" customFormat="1" ht="86.1" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B46" s="16">
         <v>37</v>
@@ -7506,12 +7506,12 @@
         <v>4</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:5" s="11" customFormat="1" ht="75.599999999999994" customHeight="1">
       <c r="A47" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47" s="16">
         <v>37</v>
@@ -7523,12 +7523,12 @@
         <v>4</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:5" s="11" customFormat="1" ht="83.7" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48" s="16">
         <v>38</v>
@@ -7540,12 +7540,12 @@
         <v>4</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:5" s="11" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="A49" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" s="16">
         <v>38</v>
@@ -7557,12 +7557,12 @@
         <v>4</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="11" customFormat="1" ht="118.95" customHeight="1">
       <c r="A50" s="47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" s="16">
         <v>39</v>
@@ -7574,12 +7574,12 @@
         <v>4</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:5" s="11" customFormat="1" ht="75.599999999999994" customHeight="1">
       <c r="A51" s="47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B51" s="16">
         <v>39</v>
@@ -7591,12 +7591,12 @@
         <v>4</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:5" s="11" customFormat="1" ht="86.1" customHeight="1">
       <c r="A52" s="49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" s="16">
         <v>40</v>
@@ -7608,12 +7608,12 @@
         <v>4</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:5" s="11" customFormat="1" ht="86.1" customHeight="1">
       <c r="A53" s="50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B53" s="16">
         <v>40</v>
@@ -7625,12 +7625,12 @@
         <v>4</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:5" s="11" customFormat="1" ht="52.2" customHeight="1">
       <c r="A54" s="51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B54" s="32">
         <v>66</v>
@@ -7645,33 +7645,33 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="53" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="34"/>
     <cfRule type="duplicateValues" dxfId="49" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="37" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:A12">
     <cfRule type="duplicateValues" dxfId="30" priority="20"/>
@@ -7689,20 +7689,20 @@
     <cfRule type="duplicateValues" dxfId="26" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A28">
-    <cfRule type="duplicateValues" dxfId="25" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
     <cfRule type="duplicateValues" dxfId="23" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29">
     <cfRule type="duplicateValues" dxfId="19" priority="4"/>
     <cfRule type="duplicateValues" dxfId="18" priority="5"/>
     <cfRule type="duplicateValues" dxfId="17" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:A40">
     <cfRule type="duplicateValues" dxfId="13" priority="53"/>
@@ -7712,8 +7712,8 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:A49">
     <cfRule type="duplicateValues" dxfId="8" priority="46"/>
